--- a/public/exports-with-coowners/65113015.xlsx
+++ b/public/exports-with-coowners/65113015.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-with-coowners/65113015.xlsx
+++ b/public/exports-with-coowners/65113015.xlsx
@@ -6514,12 +6514,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873659</t>
+          <t xml:space="preserve">311873660</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artelia A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M87" t="inlineStr">

--- a/public/exports-with-coowners/65113015.xlsx
+++ b/public/exports-with-coowners/65113015.xlsx
@@ -6514,12 +6514,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873660</t>
+          <t xml:space="preserve">311873659</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Artelia A/S</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
